--- a/api/templates/device_utilization/uk.xlsx
+++ b/api/templates/device_utilization/uk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10309"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\device_utilization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_utilization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E875C9C-602B-4CD2-A867-5EB7CBCD3623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6F0A9F-2BC4-1445-978D-2716E5668327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Коефіцієнт використання" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -123,19 +123,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,48 +528,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.8984375" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>1</v>
       </c>
     </row>

--- a/api/templates/device_utilization/uk.xlsx
+++ b/api/templates/device_utilization/uk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\device_utilization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_utilization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E875C9C-602B-4CD2-A867-5EB7CBCD3623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCADB8E-2D89-8D4C-985A-4C0BBF4AC076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="760" windowWidth="23260" windowHeight="13180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Коефіцієнт використання" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>Області: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Відсотки по пристроях не зважені відповідно до їхньої потужності. Тому середнє значення цих показників може відрізнятися від загального відсотка, що відображається в системі.</t>
   </si>
 </sst>
 </file>
@@ -128,7 +131,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -136,6 +139,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,53 +519,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.8984375" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:I4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/api/templates/device_utilization/uk.xlsx
+++ b/api/templates/device_utilization/uk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_utilization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCADB8E-2D89-8D4C-985A-4C0BBF4AC076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4665F279-D195-C44E-8547-523652907F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-100" yWindow="760" windowWidth="23260" windowHeight="13180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -52,6 +52,12 @@
   </si>
   <si>
     <t>Відсотки по пристроях не зважені відповідно до їхньої потужності. Тому середнє значення цих показників може відрізнятися від загального відсотка, що відображається в системі.</t>
+  </si>
+  <si>
+    <t>&lt;dailyTestCapacity&gt;</t>
+  </si>
+  <si>
+    <t>Добова потужність</t>
   </si>
 </sst>
 </file>
@@ -131,7 +137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -142,6 +148,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,19 +583,25 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/device_utilization/uk.xlsx
+++ b/api/templates/device_utilization/uk.xlsx
@@ -1,98 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_utilization/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4665F279-D195-C44E-8547-523652907F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="760" windowWidth="23260" windowHeight="13180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="760" windowWidth="23260" windowHeight="13180"/>
   </bookViews>
   <sheets>
-    <sheet name="Коефіцієнт використання" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Коефіцієнт використання" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>Коефіцієнт використання пристрою</t>
+  </si>
+  <si>
+    <t>Дати: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Відсотки по пристроях не зважені відповідно до їхньої потужності. Тому середнє значення цих показників може відрізнятися від загального відсотка, що відображається в системі.</t>
+  </si>
+  <si>
+    <t>Області: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Райони: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>Сайти: &lt;Sites&gt;</t>
+  </si>
   <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Пристрій</t>
+  </si>
+  <si>
+    <t>Сайт</t>
+  </si>
+  <si>
+    <t>Добова потужність</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
-    <t>Дати: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>Райони: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>Сайти: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t>Коефіцієнт використання пристрою</t>
-  </si>
-  <si>
-    <t>Пристрій</t>
-  </si>
-  <si>
-    <t>Області: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>Відсотки по пристроях не зважені відповідно до їхньої потужності. Тому середнє значення цих показників може відрізнятися від загального відсотка, що відображається в системі.</t>
+    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>&lt;dailyTestCapacity&gt;</t>
-  </si>
-  <si>
-    <t>Добова потужність</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -118,143 +113,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD7D7D7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="0"/>
-    </tableStyle>
-  </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -528,87 +417,103 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="5" t="s">
+    <row r="7" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/device_utilization/uk.xlsx
+++ b/api/templates/device_utilization/uk.xlsx
@@ -1,98 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="760" windowWidth="23260" windowHeight="13180"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-100" yWindow="760" windowWidth="23260" windowHeight="13180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Коефіцієнт використання" state="visible" r:id="rId4"/>
+    <sheet name="Коефіцієнт використання" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Коефіцієнт використання пристрою</t>
-  </si>
-  <si>
-    <t>Дати: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>Відсотки по пристроях не зважені відповідно до їхньої потужності. Тому середнє значення цих показників може відрізнятися від загального відсотка, що відображається в системі.</t>
-  </si>
-  <si>
-    <t>Області: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>Райони: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>Сайти: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Table&gt;</t>
-  </si>
-  <si>
-    <t>Пристрій</t>
-  </si>
-  <si>
-    <t>Сайт</t>
-  </si>
-  <si>
-    <t>Добова потужність</t>
-  </si>
-  <si>
-    <t>&lt;name&gt;</t>
-  </si>
-  <si>
-    <t>&lt;siteName&gt;</t>
-  </si>
-  <si>
-    <t>&lt;dailyTestCapacity&gt;</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
       <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
       <color rgb="FF000000"/>
-      <family val="2"/>
       <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <charset val="1"/>
+      <family val="2"/>
       <color rgb="FF000000"/>
-      <family val="2"/>
       <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
       <charset val="1"/>
       <family val="2"/>
+      <b val="1"/>
       <sz val="12"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -104,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -119,39 +76,106 @@
       <bottom style="medium"/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -417,103 +441,112 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="16" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="31.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="31.83" customWidth="1" min="2" max="2"/>
+    <col width="10.16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Коефіцієнт використання пристрою</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Дати: &lt;Dates&gt;</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Відсотки по пристроях не зважені відповідно до їхньої потужності. Тому середнє значення цих показників може відрізнятися від загального відсотка, що відображається в системі.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>&lt;Table&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Сайт</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Пристрій</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Добова потужність</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customFormat="1" s="6">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>&lt;siteName&gt;</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>&lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>&lt;dailyTestCapacity&gt;</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/device_utilization/uk.xlsx
+++ b/api/templates/device_utilization/uk.xlsx
@@ -1,58 +1,107 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-100" yWindow="760" windowWidth="23260" windowHeight="13180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-100" yWindow="760" windowWidth="23260" windowHeight="13180" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Коефіцієнт використання" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet sheetId="1" name="Коефіцієнт використання" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="171027" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>Коефіцієнт використання пристрою</t>
+  </si>
+  <si>
+    <t>Дати: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Відсотки по пристроях не зважені відповідно до їхньої потужності. Тому середнє значення цих показників може відрізнятися від загального відсотка, що відображається в системі.</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+  </si>
+  <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Table&gt;</t>
+  </si>
+  <si>
+    <t>Сайт</t>
+  </si>
+  <si>
+    <t>Пристрій</t>
+  </si>
+  <si>
+    <t>Добова потужність</t>
+  </si>
+  <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;name&gt;</t>
+  </si>
+  <si>
+    <t>&lt;dailyTestCapacity&gt;</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="16"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <charset val="1"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="16"/>
-    </font>
-    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -81,101 +130,42 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -441,112 +431,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="16" customHeight="1" outlineLevelRow="0"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11" customHeight="1"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="31.83" customWidth="1" min="2" max="2"/>
-    <col width="10.16" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="31.83" customWidth="1"/>
+    <col min="3" max="3" width="10.16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Коефіцієнт використання пристрою</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Дати: &lt;Dates&gt;</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Відсотки по пристроях не зважені відповідно до їхньої потужності. Тому середнє значення цих показників може відрізнятися від загального відсотка, що відображається в системі.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>&lt;Table&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Сайт</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Пристрій</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Добова потужність</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="6">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>&lt;siteName&gt;</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>&lt;name&gt;</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>&lt;dailyTestCapacity&gt;</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+    </row>
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/device_utilization/uk.xlsx
+++ b/api/templates/device_utilization/uk.xlsx
@@ -142,9 +142,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>

--- a/api/templates/device_utilization/uk.xlsx
+++ b/api/templates/device_utilization/uk.xlsx
@@ -34,7 +34,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Виведені з експлуатації пристрої: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -142,7 +142,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
